--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0147C24-4E3B-4AF6-B916-9F42E93A6E4C}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{047D29C5-2E99-4724-9A44-84466D066E1D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
     <sheet name="Matchups" sheetId="2" r:id="rId2"/>
     <sheet name="Cup" sheetId="3" r:id="rId3"/>
     <sheet name="Waivers" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="6" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -358,6 +362,42 @@
   </si>
   <si>
     <t>nictrn</t>
+  </si>
+  <si>
+    <t>Viktor Mykolenko</t>
+  </si>
+  <si>
+    <t>Josh King</t>
+  </si>
+  <si>
+    <t>Malick Yalcouye</t>
+  </si>
+  <si>
+    <t>Jack Rudoni</t>
+  </si>
+  <si>
+    <t>Murillo</t>
+  </si>
+  <si>
+    <t>Daichi Kamada</t>
+  </si>
+  <si>
+    <t>Regan Slater</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Max_Points</t>
+  </si>
+  <si>
+    <t>Sum of Home_team_best_lineup</t>
+  </si>
+  <si>
+    <t>Sum of Away_team_best_lineup</t>
   </si>
 </sst>
 </file>
@@ -402,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -415,6 +455,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,6 +472,474 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Not Nico" refreshedDate="46280.663731828703" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="17" xr:uid="{C533F88C-EC2B-4150-ACB7-2F4E1995CCF2}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:G1048576" sheet="Matchups"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="home_team_id" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="8" count="9">
+        <n v="1"/>
+        <n v="5"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="4"/>
+        <n v="6"/>
+        <n v="3"/>
+        <n v="2"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="away_team_id" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="8" count="9">
+        <n v="3"/>
+        <n v="4"/>
+        <n v="2"/>
+        <n v="6"/>
+        <n v="8"/>
+        <n v="5"/>
+        <n v="7"/>
+        <n v="1"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Home_team_points" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="62.25" maxValue="166.5" count="17">
+        <n v="99.5"/>
+        <n v="107.5"/>
+        <n v="79.75"/>
+        <n v="118.25"/>
+        <n v="75"/>
+        <n v="106"/>
+        <n v="103.25"/>
+        <n v="157.5"/>
+        <n v="62.25"/>
+        <n v="96"/>
+        <n v="96.25"/>
+        <n v="97.75"/>
+        <n v="107.75"/>
+        <n v="166.5"/>
+        <n v="136.75"/>
+        <n v="90.75"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Away_team_points" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="71.5" maxValue="131.25"/>
+    </cacheField>
+    <cacheField name="Home_team_best_lineup" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="75" maxValue="171"/>
+    </cacheField>
+    <cacheField name="Away_team_best_lineup" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="79.5" maxValue="135.5" count="13">
+        <n v="83.75"/>
+        <n v="88.25"/>
+        <n v="79.5"/>
+        <n v="129.75"/>
+        <n v="127.75"/>
+        <n v="123.25"/>
+        <n v="100.5"/>
+        <n v="135.5"/>
+        <n v="120.75"/>
+        <n v="116.75"/>
+        <n v="124.75"/>
+        <n v="116.5"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Week" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="3"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="17">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="71.5"/>
+    <n v="149.75"/>
+    <x v="0"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="80.5"/>
+    <n v="115.25"/>
+    <x v="1"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="76"/>
+    <n v="101"/>
+    <x v="2"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="111.25"/>
+    <n v="132"/>
+    <x v="3"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="4"/>
+    <n v="97.25"/>
+    <n v="94.75"/>
+    <x v="4"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="5"/>
+    <n v="98.25"/>
+    <n v="135.25"/>
+    <x v="5"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="6"/>
+    <n v="95"/>
+    <n v="145.25"/>
+    <x v="6"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="7"/>
+    <n v="131.25"/>
+    <n v="171"/>
+    <x v="7"/>
+    <n v="2"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="8"/>
+    <n v="103.75"/>
+    <n v="75"/>
+    <x v="8"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="9"/>
+    <n v="101.75"/>
+    <n v="134"/>
+    <x v="9"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="4"/>
+    <x v="10"/>
+    <n v="92.5"/>
+    <n v="104.75"/>
+    <x v="10"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="3"/>
+    <x v="11"/>
+    <n v="91.5"/>
+    <n v="132.25"/>
+    <x v="11"/>
+    <n v="3"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="12"/>
+    <n v="80.75"/>
+    <m/>
+    <x v="12"/>
+    <m/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="13"/>
+    <n v="96"/>
+    <m/>
+    <x v="12"/>
+    <m/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="14"/>
+    <n v="78.5"/>
+    <m/>
+    <x v="12"/>
+    <m/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="5"/>
+    <x v="15"/>
+    <n v="78.25"/>
+    <m/>
+    <x v="12"/>
+    <m/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="16"/>
+    <m/>
+    <m/>
+    <x v="12"/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04013F23-70FF-498B-9A36-6D46F762FCC0}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A14:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="8"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="9">
+        <item x="7"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="8"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="17">
+        <item x="8"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="16"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="13">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="9"/>
+        <item x="8"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="12"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Away_team_best_lineup" fld="5" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D0863126-9418-4AD3-9369-A24D7428D316}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A1:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="8"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="17">
+        <item x="8"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="15"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="16"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Home_team_best_lineup" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -729,14 +1239,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE574477-F8B8-4C54-8D52-90DE47CC4CEE}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -752,8 +1264,11 @@
       <c r="E1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -769,8 +1284,11 @@
       <c r="E2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>433.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -786,8 +1304,11 @@
       <c r="E3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>456.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -803,8 +1324,11 @@
       <c r="E4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>406.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -820,8 +1344,11 @@
       <c r="E5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <v>540.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -837,8 +1364,11 @@
       <c r="E6" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -854,8 +1384,11 @@
       <c r="E7" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <v>556.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -871,8 +1404,11 @@
       <c r="E8" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <v>525.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -887,6 +1423,9 @@
       </c>
       <c r="E9" t="s">
         <v>74</v>
+      </c>
+      <c r="F9">
+        <v>490.25</v>
       </c>
     </row>
   </sheetData>
@@ -896,10 +1435,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBDA112-4455-493F-9D63-4B72BBDFDC28}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="7" width="16.28515625" style="3" customWidth="1"/>
+    <col min="1" max="4" width="16.28515625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" style="3" customWidth="1"/>
+    <col min="6" max="7" width="16.28515625" style="3" customWidth="1"/>
     <col min="8" max="8" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1200,6 +1741,98 @@
       </c>
       <c r="G13" s="3">
         <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>2</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>107.75</v>
+      </c>
+      <c r="D14" s="3">
+        <v>80.75</v>
+      </c>
+      <c r="E14" s="3">
+        <v>121.75</v>
+      </c>
+      <c r="F14" s="3">
+        <v>114</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>4</v>
+      </c>
+      <c r="B15" s="3">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3">
+        <v>166.5</v>
+      </c>
+      <c r="D15" s="3">
+        <v>96</v>
+      </c>
+      <c r="E15" s="3">
+        <v>183</v>
+      </c>
+      <c r="F15" s="3">
+        <v>139.5</v>
+      </c>
+      <c r="G15" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>7</v>
+      </c>
+      <c r="B16" s="3">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3">
+        <v>136.75</v>
+      </c>
+      <c r="D16" s="3">
+        <v>78.5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>162.25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>105.75</v>
+      </c>
+      <c r="G16" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>3</v>
+      </c>
+      <c r="B17" s="3">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3">
+        <v>90.75</v>
+      </c>
+      <c r="D17" s="3">
+        <v>78.25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>117.25</v>
+      </c>
+      <c r="F17" s="3">
+        <v>99.5</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1444,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE21E41-8143-4B31-AF43-B1572AB93726}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
@@ -2083,8 +2716,461 @@
         <v>5</v>
       </c>
     </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2</v>
+      </c>
+      <c r="B38">
+        <v>37</v>
+      </c>
+      <c r="C38" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>8</v>
+      </c>
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D39" t="s">
+        <v>108</v>
+      </c>
+      <c r="E39">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>8</v>
+      </c>
+      <c r="B40">
+        <v>39</v>
+      </c>
+      <c r="C40" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D40" t="s">
+        <v>109</v>
+      </c>
+      <c r="E40">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="B41">
+        <v>40</v>
+      </c>
+      <c r="C41" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D41" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>5</v>
+      </c>
+      <c r="B42">
+        <v>41</v>
+      </c>
+      <c r="C42" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D42" t="s">
+        <v>111</v>
+      </c>
+      <c r="E42">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>8</v>
+      </c>
+      <c r="B43">
+        <v>42</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E43">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>5</v>
+      </c>
+      <c r="B44">
+        <v>43</v>
+      </c>
+      <c r="C44" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D44" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>5</v>
+      </c>
+      <c r="B45">
+        <v>44</v>
+      </c>
+      <c r="C45" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D45" t="s">
+        <v>113</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D46" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D47" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A72ED84-60A7-4A50-A5DA-14C897D6AA35}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="30.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6">
+        <v>319.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6">
+        <v>132.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6">
+        <v>104.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6">
+        <v>269.25</v>
+      </c>
+      <c r="D5">
+        <f>GETPIVOTDATA("Home_team_best_lineup",A1,"home_team_id",1)-GETPIVOTDATA("Away_team_best_lineup",A14,"away_team_id",1)</f>
+        <v>319.5</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(A2,Teams!A:F,6,0)</f>
+        <v>433.5</v>
+      </c>
+      <c r="F5">
+        <f>E5-D5</f>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6">
+        <v>115.25</v>
+      </c>
+      <c r="D6">
+        <f>GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",2)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",2)</f>
+        <v>335</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(A3,Teams!A:F,6,0)</f>
+        <v>456.75</v>
+      </c>
+      <c r="F6">
+        <f>E6-D6</f>
+        <v>121.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6">
+        <v>171</v>
+      </c>
+      <c r="D7">
+        <f>GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",3)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",3)</f>
+        <v>289</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP(A4,Teams!A:F,6,0)</f>
+        <v>406.25</v>
+      </c>
+      <c r="F7">
+        <f t="shared" ref="F6:F12" si="0">E7-D7</f>
+        <v>117.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6">
+        <v>246.25</v>
+      </c>
+      <c r="D8">
+        <f>GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",4)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",4)</f>
+        <v>357.5</v>
+      </c>
+      <c r="E8">
+        <f>VLOOKUP(A5,Teams!A:F,6,0)</f>
+        <v>540.5</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>132</v>
+      </c>
+      <c r="D9">
+        <f>GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",5)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",5)</f>
+        <v>371.5</v>
+      </c>
+      <c r="E9">
+        <f>VLOOKUP(A6,Teams!A:F,6,0)</f>
+        <v>471</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="D10">
+        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",6)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",6)</f>
+        <v>417.25</v>
+      </c>
+      <c r="E10">
+        <f>VLOOKUP(A7,Teams!A:F,6,0)</f>
+        <v>556.75</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>139.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1490.25</v>
+      </c>
+      <c r="D11">
+        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",7)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",7)</f>
+        <v>363</v>
+      </c>
+      <c r="E11">
+        <f>VLOOKUP(A8,Teams!A:F,6,0)</f>
+        <v>525.25</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>162.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <f>+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",8)+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",8)</f>
+        <v>384.5</v>
+      </c>
+      <c r="E12">
+        <f>VLOOKUP(A9,Teams!A:F,6,0)</f>
+        <v>490.25</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>105.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" s="6">
+        <v>202.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>3</v>
+      </c>
+      <c r="B17" s="6">
+        <v>184.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>4</v>
+      </c>
+      <c r="B18" s="6">
+        <v>88.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6">
+        <v>256.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>6</v>
+      </c>
+      <c r="B20" s="6">
+        <v>246.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>7</v>
+      </c>
+      <c r="B21" s="6">
+        <v>116.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>8</v>
+      </c>
+      <c r="B22" s="6">
+        <v>252.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1347</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/league-data.xlsx
+++ b/league-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f9ba65d159c4500d/Desktop/Nicolas Folder/Work/Excel/Fantasy Soccer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{047D29C5-2E99-4724-9A44-84466D066E1D}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{5C16C4EC-6E79-4FAA-ADB2-319885C4C91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFFA068E-A0B8-417D-9FC6-CBCECDF72336}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
+    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{D9336D12-E46F-4D57-BE81-BE832F455B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Teams" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId6"/>
+    <pivotCache cacheId="10" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="124">
   <si>
     <t>ID</t>
   </si>
@@ -398,6 +398,21 @@
   </si>
   <si>
     <t>Sum of Away_team_best_lineup</t>
+  </si>
+  <si>
+    <t>Brian Brobbey</t>
+  </si>
+  <si>
+    <t>Jaidon Anthony</t>
+  </si>
+  <si>
+    <t>Antonee Robinson</t>
+  </si>
+  <si>
+    <t>Zion Suzuki</t>
+  </si>
+  <si>
+    <t>Jannik Schuster</t>
   </si>
 </sst>
 </file>
@@ -455,8 +470,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,7 +490,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Not Nico" refreshedDate="46280.663731828703" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="17" xr:uid="{C533F88C-EC2B-4150-ACB7-2F4E1995CCF2}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Not Nico" refreshedDate="46285.873981249999" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="21" xr:uid="{C533F88C-EC2B-4150-ACB7-2F4E1995CCF2}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G1048576" sheet="Matchups"/>
   </cacheSource>
@@ -507,51 +522,19 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Home_team_points" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="62.25" maxValue="166.5" count="17">
-        <n v="99.5"/>
-        <n v="107.5"/>
-        <n v="79.75"/>
-        <n v="118.25"/>
-        <n v="75"/>
-        <n v="106"/>
-        <n v="103.25"/>
-        <n v="157.5"/>
-        <n v="62.25"/>
-        <n v="96"/>
-        <n v="96.25"/>
-        <n v="97.75"/>
-        <n v="107.75"/>
-        <n v="166.5"/>
-        <n v="136.75"/>
-        <n v="90.75"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="62.25" maxValue="166.5"/>
     </cacheField>
     <cacheField name="Away_team_points" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="71.5" maxValue="131.25"/>
     </cacheField>
     <cacheField name="Home_team_best_lineup" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="75" maxValue="171"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="75" maxValue="183"/>
     </cacheField>
     <cacheField name="Away_team_best_lineup" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="79.5" maxValue="135.5" count="13">
-        <n v="83.75"/>
-        <n v="88.25"/>
-        <n v="79.5"/>
-        <n v="129.75"/>
-        <n v="127.75"/>
-        <n v="123.25"/>
-        <n v="100.5"/>
-        <n v="135.5"/>
-        <n v="120.75"/>
-        <n v="116.75"/>
-        <n v="124.75"/>
-        <n v="116.5"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="79.5" maxValue="139.5"/>
     </cacheField>
     <cacheField name="Week" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="3"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -563,290 +546,201 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="17">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="21">
   <r>
     <x v="0"/>
     <x v="0"/>
-    <x v="0"/>
+    <n v="99.5"/>
     <n v="71.5"/>
     <n v="149.75"/>
-    <x v="0"/>
+    <n v="83.75"/>
     <n v="1"/>
   </r>
   <r>
     <x v="1"/>
     <x v="1"/>
-    <x v="1"/>
+    <n v="107.5"/>
     <n v="80.5"/>
     <n v="115.25"/>
-    <x v="1"/>
+    <n v="88.25"/>
     <n v="1"/>
   </r>
   <r>
     <x v="2"/>
     <x v="2"/>
-    <x v="2"/>
+    <n v="79.75"/>
     <n v="76"/>
     <n v="101"/>
-    <x v="2"/>
+    <n v="79.5"/>
     <n v="1"/>
   </r>
   <r>
     <x v="3"/>
     <x v="3"/>
-    <x v="3"/>
+    <n v="118.25"/>
     <n v="111.25"/>
     <n v="132"/>
-    <x v="3"/>
+    <n v="129.75"/>
     <n v="1"/>
   </r>
   <r>
     <x v="0"/>
     <x v="4"/>
-    <x v="4"/>
+    <n v="75"/>
     <n v="97.25"/>
     <n v="94.75"/>
-    <x v="4"/>
+    <n v="127.75"/>
     <n v="2"/>
   </r>
   <r>
     <x v="4"/>
     <x v="2"/>
-    <x v="5"/>
+    <n v="106"/>
     <n v="98.25"/>
     <n v="135.25"/>
-    <x v="5"/>
+    <n v="123.25"/>
     <n v="2"/>
   </r>
   <r>
     <x v="2"/>
     <x v="0"/>
-    <x v="6"/>
+    <n v="103.25"/>
     <n v="95"/>
     <n v="145.25"/>
-    <x v="6"/>
+    <n v="100.5"/>
     <n v="2"/>
   </r>
   <r>
     <x v="5"/>
     <x v="5"/>
-    <x v="7"/>
+    <n v="157.5"/>
     <n v="131.25"/>
     <n v="171"/>
-    <x v="7"/>
+    <n v="135.5"/>
     <n v="2"/>
   </r>
   <r>
     <x v="0"/>
     <x v="5"/>
-    <x v="8"/>
+    <n v="62.25"/>
     <n v="103.75"/>
     <n v="75"/>
-    <x v="8"/>
+    <n v="120.75"/>
     <n v="3"/>
   </r>
   <r>
     <x v="4"/>
     <x v="6"/>
-    <x v="9"/>
+    <n v="96"/>
     <n v="101.75"/>
     <n v="134"/>
-    <x v="9"/>
+    <n v="116.75"/>
     <n v="3"/>
   </r>
   <r>
     <x v="6"/>
     <x v="4"/>
-    <x v="10"/>
+    <n v="96.25"/>
     <n v="92.5"/>
     <n v="104.75"/>
-    <x v="10"/>
+    <n v="124.75"/>
     <n v="3"/>
   </r>
   <r>
     <x v="7"/>
     <x v="3"/>
-    <x v="11"/>
+    <n v="97.75"/>
     <n v="91.5"/>
     <n v="132.25"/>
-    <x v="11"/>
+    <n v="116.5"/>
     <n v="3"/>
   </r>
   <r>
     <x v="7"/>
     <x v="7"/>
-    <x v="12"/>
+    <n v="107.75"/>
     <n v="80.75"/>
-    <m/>
-    <x v="12"/>
-    <m/>
+    <n v="121.75"/>
+    <n v="114"/>
+    <n v="4"/>
   </r>
   <r>
     <x v="4"/>
     <x v="3"/>
-    <x v="13"/>
+    <n v="166.5"/>
     <n v="96"/>
-    <m/>
-    <x v="12"/>
-    <m/>
+    <n v="183"/>
+    <n v="139.5"/>
+    <n v="4"/>
   </r>
   <r>
     <x v="2"/>
     <x v="4"/>
-    <x v="14"/>
+    <n v="136.75"/>
     <n v="78.5"/>
-    <m/>
-    <x v="12"/>
-    <m/>
+    <n v="162.25"/>
+    <n v="105.75"/>
+    <n v="4"/>
   </r>
   <r>
     <x v="6"/>
     <x v="5"/>
-    <x v="15"/>
+    <n v="90.75"/>
     <n v="78.25"/>
+    <n v="117.25"/>
+    <n v="99.5"/>
+    <n v="4"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="7"/>
+    <n v="105"/>
+    <n v="104.25"/>
     <m/>
-    <x v="12"/>
     <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="6"/>
+    <n v="106.75"/>
+    <n v="119.5"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <n v="72.25"/>
+    <n v="122.5"/>
+    <m/>
+    <m/>
+    <n v="5"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="88.254999999999995"/>
+    <n v="91.25"/>
+    <m/>
+    <m/>
+    <n v="5"/>
   </r>
   <r>
     <x v="8"/>
     <x v="8"/>
-    <x v="16"/>
     <m/>
     <m/>
-    <x v="12"/>
+    <m/>
+    <m/>
     <m/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04013F23-70FF-498B-9A36-6D46F762FCC0}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A14:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="7">
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="8"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="9">
-        <item x="7"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="8"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="17">
-        <item x="8"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="15"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="14"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="16"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="13">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="6"/>
-        <item x="11"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="12"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Away_team_best_lineup" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D0863126-9418-4AD3-9369-A24D7428D316}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D0863126-9418-4AD3-9369-A24D7428D316}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A1:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -863,27 +757,7 @@
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="17">
-        <item x="8"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="15"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="12"/>
-        <item x="3"/>
-        <item x="14"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="16"/>
-      </items>
-    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -929,6 +803,83 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Sum of Home_team_best_lineup" fld="4" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04013F23-70FF-498B-9A36-6D46F762FCC0}" name="PivotTable2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A14:B24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="9">
+        <item x="7"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="8"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Away_team_best_lineup" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -1245,7 +1196,7 @@
     <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1285,7 +1236,7 @@
         <v>73</v>
       </c>
       <c r="F2">
-        <v>433.5</v>
+        <v>576.75</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1305,7 +1256,7 @@
         <v>74</v>
       </c>
       <c r="F3">
-        <v>456.75</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1325,7 +1276,7 @@
         <v>75</v>
       </c>
       <c r="F4">
-        <v>406.25</v>
+        <v>554.75</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1345,7 +1296,7 @@
         <v>76</v>
       </c>
       <c r="F5">
-        <v>540.5</v>
+        <v>678.5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1365,7 +1316,7 @@
         <v>78</v>
       </c>
       <c r="F6">
-        <v>471</v>
+        <v>585.75</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1385,7 +1336,7 @@
         <v>77</v>
       </c>
       <c r="F7">
-        <v>556.75</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1405,7 +1356,7 @@
         <v>77</v>
       </c>
       <c r="F8">
-        <v>525.25</v>
+        <v>663.5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1425,7 +1376,7 @@
         <v>74</v>
       </c>
       <c r="F9">
-        <v>490.25</v>
+        <v>597.75</v>
       </c>
     </row>
   </sheetData>
@@ -1435,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBDA112-4455-493F-9D63-4B72BBDFDC28}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="16.28515625" style="3" customWidth="1"/>
@@ -1833,6 +1784,98 @@
       </c>
       <c r="G17" s="3">
         <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>4</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3">
+        <v>105</v>
+      </c>
+      <c r="D18" s="3">
+        <v>104.25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>138</v>
+      </c>
+      <c r="F18" s="3">
+        <v>143.25</v>
+      </c>
+      <c r="G18" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>6</v>
+      </c>
+      <c r="B19" s="3">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3">
+        <v>106.75</v>
+      </c>
+      <c r="D19" s="3">
+        <v>119.5</v>
+      </c>
+      <c r="E19" s="3">
+        <v>139.25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>138.25</v>
+      </c>
+      <c r="G19" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>2</v>
+      </c>
+      <c r="B20" s="3">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3">
+        <v>72.25</v>
+      </c>
+      <c r="D20" s="3">
+        <v>122.5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>86.25</v>
+      </c>
+      <c r="F20" s="3">
+        <v>148.5</v>
+      </c>
+      <c r="G20" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>5</v>
+      </c>
+      <c r="B21" s="3">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3">
+        <v>88.254999999999995</v>
+      </c>
+      <c r="D21" s="3">
+        <v>91.25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>114.75</v>
+      </c>
+      <c r="F21" s="3">
+        <v>107.5</v>
+      </c>
+      <c r="G21" s="3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2120,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BE21E41-8143-4B31-AF43-B1572AB93726}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" customWidth="1"/>
@@ -2886,6 +2929,91 @@
         <v>50</v>
       </c>
     </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>5</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" s="1">
+        <v>46285</v>
+      </c>
+      <c r="D48" t="s">
+        <v>119</v>
+      </c>
+      <c r="E48">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2</v>
+      </c>
+      <c r="B49">
+        <v>48</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46285</v>
+      </c>
+      <c r="D49" t="s">
+        <v>120</v>
+      </c>
+      <c r="E49">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2</v>
+      </c>
+      <c r="B50">
+        <v>49</v>
+      </c>
+      <c r="C50" s="1">
+        <v>46285</v>
+      </c>
+      <c r="D50" t="s">
+        <v>121</v>
+      </c>
+      <c r="E50">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <v>50</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46285</v>
+      </c>
+      <c r="D51" t="s">
+        <v>122</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>5</v>
+      </c>
+      <c r="B52">
+        <v>51</v>
+      </c>
+      <c r="C52" s="1">
+        <v>46285</v>
+      </c>
+      <c r="D52" t="s">
+        <v>123</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2894,7 +3022,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A72ED84-60A7-4A50-A5DA-14C897D6AA35}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -2902,209 +3030,209 @@
     <col min="4" max="6" width="30.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="7">
         <v>319.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2">
+        <f>GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",1)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",1)</f>
+        <v>433.5</v>
+      </c>
+      <c r="D2">
+        <f>VLOOKUP(A2,Teams!A:F,6,0)</f>
+        <v>576.75</v>
+      </c>
+      <c r="E2">
+        <f>D2-C2</f>
+        <v>143.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
-        <v>132.25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="7">
+        <v>254</v>
+      </c>
+      <c r="C3">
+        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",2)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",2)</f>
+        <v>456.75</v>
+      </c>
+      <c r="D3">
+        <f>VLOOKUP(A3,Teams!A:F,6,0)</f>
+        <v>543</v>
+      </c>
+      <c r="E3">
+        <f>D3-C3</f>
+        <v>86.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
-        <v>104.75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="7">
+        <v>222</v>
+      </c>
+      <c r="C4">
+        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",3)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",3)</f>
+        <v>406.25</v>
+      </c>
+      <c r="D4">
+        <f>VLOOKUP(A4,Teams!A:F,6,0)</f>
+        <v>554.75</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E9" si="0">D4-C4</f>
+        <v>148.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
-        <v>269.25</v>
+      <c r="B5" s="7">
+        <v>452.25</v>
+      </c>
+      <c r="C5">
+        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",4)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",4)</f>
+        <v>540.5</v>
       </c>
       <c r="D5">
-        <f>GETPIVOTDATA("Home_team_best_lineup",A1,"home_team_id",1)-GETPIVOTDATA("Away_team_best_lineup",A14,"away_team_id",1)</f>
-        <v>319.5</v>
+        <f>VLOOKUP(A5,Teams!A:F,6,0)</f>
+        <v>678.5</v>
       </c>
       <c r="E5">
-        <f>VLOOKUP(A2,Teams!A:F,6,0)</f>
-        <v>433.5</v>
-      </c>
-      <c r="F5">
-        <f>E5-D5</f>
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>115.25</v>
       </c>
+      <c r="C6">
+        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",5)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",5)</f>
+        <v>471</v>
+      </c>
       <c r="D6">
-        <f>GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",2)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",2)</f>
-        <v>335</v>
+        <f>VLOOKUP(A6,Teams!A:F,6,0)</f>
+        <v>585.75</v>
       </c>
       <c r="E6">
-        <f>VLOOKUP(A3,Teams!A:F,6,0)</f>
-        <v>456.75</v>
-      </c>
-      <c r="F6">
-        <f>E6-D6</f>
-        <v>121.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>114.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>171</v>
       </c>
+      <c r="C7">
+        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",6)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",6)</f>
+        <v>556.75</v>
+      </c>
       <c r="D7">
-        <f>GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",3)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",3)</f>
-        <v>289</v>
+        <f>VLOOKUP(A7,Teams!A:F,6,0)</f>
+        <v>696</v>
       </c>
       <c r="E7">
-        <f>VLOOKUP(A4,Teams!A:F,6,0)</f>
-        <v>406.25</v>
-      </c>
-      <c r="F7">
-        <f t="shared" ref="F6:F12" si="0">E7-D7</f>
-        <v>117.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>139.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
-        <v>246.25</v>
+      <c r="B8" s="7">
+        <v>408.5</v>
+      </c>
+      <c r="C8">
+        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",7)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",7)</f>
+        <v>525.25</v>
       </c>
       <c r="D8">
-        <f>GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",4)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",4)</f>
-        <v>357.5</v>
+        <f>VLOOKUP(A8,Teams!A:F,6,0)</f>
+        <v>663.5</v>
       </c>
       <c r="E8">
-        <f>VLOOKUP(A5,Teams!A:F,6,0)</f>
-        <v>540.5</v>
-      </c>
-      <c r="F8">
         <f t="shared" si="0"/>
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>138.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>132</v>
       </c>
+      <c r="C9">
+        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",8)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",8)</f>
+        <v>490.25</v>
+      </c>
       <c r="D9">
-        <f>GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",5)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",5)</f>
-        <v>371.5</v>
+        <f>VLOOKUP(A9,Teams!A:F,6,0)</f>
+        <v>597.75</v>
       </c>
       <c r="E9">
-        <f>VLOOKUP(A6,Teams!A:F,6,0)</f>
-        <v>471</v>
-      </c>
-      <c r="F9">
         <f t="shared" si="0"/>
-        <v>99.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>107.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>114</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="D10">
-        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",6)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",6)</f>
-        <v>417.25</v>
-      </c>
-      <c r="E10">
-        <f>VLOOKUP(A7,Teams!A:F,6,0)</f>
-        <v>556.75</v>
-      </c>
-      <c r="F10">
-        <f t="shared" si="0"/>
-        <v>139.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="6">
-        <v>1490.25</v>
-      </c>
-      <c r="D11">
-        <f>+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",7)+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",7)</f>
-        <v>363</v>
-      </c>
-      <c r="E11">
-        <f>VLOOKUP(A8,Teams!A:F,6,0)</f>
-        <v>525.25</v>
-      </c>
-      <c r="F11">
-        <f t="shared" si="0"/>
-        <v>162.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D12">
-        <f>+GETPIVOTDATA("Away_team_best_lineup",$A$14,"away_team_id",8)+GETPIVOTDATA("Home_team_best_lineup",$A$1,"home_team_id",8)</f>
-        <v>384.5</v>
-      </c>
-      <c r="E12">
-        <f>VLOOKUP(A9,Teams!A:F,6,0)</f>
-        <v>490.25</v>
-      </c>
-      <c r="F12">
-        <f t="shared" si="0"/>
-        <v>105.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="B11" s="7">
+        <v>2074.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
       <c r="B14" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1</v>
       </c>
-      <c r="B15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>202.75</v>
       </c>
     </row>
@@ -3112,7 +3240,7 @@
       <c r="A17">
         <v>3</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>184.25</v>
       </c>
     </row>
@@ -3120,7 +3248,7 @@
       <c r="A18">
         <v>4</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>88.25</v>
       </c>
     </row>
@@ -3128,23 +3256,23 @@
       <c r="A19">
         <v>5</v>
       </c>
-      <c r="B19" s="6">
-        <v>256.25</v>
+      <c r="B19" s="7">
+        <v>355.75</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>6</v>
       </c>
-      <c r="B20" s="6">
-        <v>246.25</v>
+      <c r="B20" s="7">
+        <v>385.75</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>7</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="7">
         <v>116.75</v>
       </c>
     </row>
@@ -3152,22 +3280,22 @@
       <c r="A22">
         <v>8</v>
       </c>
-      <c r="B22" s="6">
-        <v>252.5</v>
+      <c r="B22" s="7">
+        <v>358.25</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>114</v>
       </c>
-      <c r="B23" s="6"/>
+      <c r="B23" s="7"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>115</v>
       </c>
-      <c r="B24" s="6">
-        <v>1347</v>
+      <c r="B24" s="7">
+        <v>1805.75</v>
       </c>
     </row>
   </sheetData>
